--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484051_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484051_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5121</v>
+        <v>6.7922</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0079</v>
+        <v>3.0586</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5042</v>
+        <v>3.7336</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8788</v>
+        <v>3.9204</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4848</v>
+        <v>2.9992</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3941</v>
+        <v>0.9212</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2267</v>
+        <v>3.116</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8587</v>
+        <v>3.0306</v>
       </c>
       <c r="L2" t="n">
-        <v>1.368</v>
+        <v>0.0854</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3479</v>
+        <v>0.8044</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3739</v>
+        <v>-0.0314</v>
       </c>
       <c r="O2" t="n">
-        <v>0.026</v>
+        <v>0.8357</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>4.645</v>
+        <v>1.5545</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3638</v>
+        <v>0.4026</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2812</v>
+        <v>1.1519</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.0118</v>
+        <v>-0.0713</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4012</v>
+        <v>0.532</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4129</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3856</v>
+        <v>5.5466</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7922</v>
+        <v>4.7438</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5933</v>
+        <v>0.8028</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9204</v>
+        <v>3.8788</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9992</v>
+        <v>2.4848</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9212</v>
+        <v>1.3941</v>
       </c>
       <c r="J3" t="n">
-        <v>3.116</v>
+        <v>4.2267</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0306</v>
+        <v>2.8587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0854</v>
+        <v>1.368</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8044</v>
+        <v>-0.3479</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0314</v>
+        <v>-0.3739</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8357</v>
+        <v>0.026</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1478</v>
+        <v>2.6796</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1362</v>
+        <v>1.0998</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0116</v>
+        <v>1.5798</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0713</v>
+        <v>-1.0118</v>
       </c>
       <c r="W3" t="n">
-        <v>0.532</v>
+        <v>1.4012</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6032</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.485</v>
+        <v>5.4401</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3391</v>
+        <v>3.0136</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1459</v>
+        <v>2.4265</v>
       </c>
       <c r="G4" t="n">
         <v>3.1741</v>
@@ -766,13 +766,13 @@
         <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4932</v>
+        <v>1.4482</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2946</v>
+        <v>0.3799</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7877999999999999</v>
+        <v>1.0683</v>
       </c>
       <c r="V4" t="n">
         <v>1.8097</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0903</v>
+        <v>3.4997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0101</v>
+        <v>-0.1316</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0802</v>
+        <v>3.6313</v>
       </c>
       <c r="G5" t="n">
         <v>0.0491</v>
@@ -844,13 +844,13 @@
         <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5688</v>
+        <v>1.9782</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3856</v>
+        <v>0.2439</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1832</v>
+        <v>1.7343</v>
       </c>
       <c r="V5" t="n">
         <v>1.4724</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>S. BACHIOCHI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7296</v>
+        <v>0.7812</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4315</v>
+        <v>0.0377</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7018</v>
+        <v>0.7435</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2501</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7812</v>
+        <v>0.3627</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5312</v>
+        <v>0.4483</v>
       </c>
       <c r="J6" t="n">
-        <v>1.25</v>
+        <v>0.0603</v>
       </c>
       <c r="K6" t="n">
-        <v>1.25</v>
+        <v>0.0202</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>0.7507</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4688</v>
+        <v>0.3425</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5312</v>
+        <v>0.4081</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2731</v>
+        <v>-0.2282</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1734</v>
+        <v>-0.0227</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0998</v>
+        <v>-0.2055</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. BACHIOCHI</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.595</v>
+        <v>0.7628</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0644</v>
+        <v>-0.5974</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6594</v>
+        <v>1.3602</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8110000000000001</v>
+        <v>-0.7823</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3627</v>
+        <v>-0.4234</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4483</v>
+        <v>-0.3589</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0603</v>
+        <v>-1.6901</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>-0.3725</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>-1.3177</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7507</v>
+        <v>0.9079</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3425</v>
+        <v>-0.0509</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4081</v>
+        <v>0.9588</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4144</v>
+        <v>-0.2565</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1247</v>
+        <v>-0.3797</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2897</v>
+        <v>0.1232</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>A. MESA RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4848</v>
+        <v>0.1984</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9035</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3883</v>
+        <v>0.1984</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7823</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4234</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3589</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6901</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3725</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3177</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9079</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0509</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9588</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5346</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6858</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1512</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MESA RUIZ</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1984</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1984</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.2501</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.7812</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.5312</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.4688</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.5312</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
         <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.4591</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1559</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.98</v>
+        <v>-0.0176</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0983</v>
+        <v>-0.2864</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1184</v>
+        <v>0.2687</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9156</v>
+        <v>0.0231</v>
       </c>
       <c r="H10" t="n">
-        <v>0.549</v>
+        <v>-0.6959</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3666</v>
+        <v>0.719</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2207</v>
+        <v>-0.2864</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7311</v>
+        <v>-0.1762</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4896</v>
+        <v>-0.1103</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3051</v>
+        <v>0.3095</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1821</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.123</v>
+        <v>0.8292</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2409</v>
+        <v>0.1658</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5498</v>
+        <v>0.0001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3089</v>
+        <v>0.1657</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4724</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0569</v>
+        <v>-0.1255</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9609</v>
+        <v>-0.3841</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.096</v>
+        <v>0.2586</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0231</v>
+        <v>0.9156</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6959</v>
+        <v>0.549</v>
       </c>
       <c r="I11" t="n">
-        <v>0.719</v>
+        <v>0.3666</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2864</v>
+        <v>1.2207</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1762</v>
+        <v>0.7311</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1103</v>
+        <v>0.4896</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3095</v>
+        <v>-0.3051</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.1821</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8292</v>
+        <v>-0.123</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6744</v>
+        <v>0.1644</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.199</v>
+        <v>0.4491</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6032</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0602</v>
+        <v>-2.0322</v>
       </c>
       <c r="E12" t="n">
         <v>-0.8069</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2533</v>
+        <v>-1.2253</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7559</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3044</v>
+        <v>-0.2763</v>
       </c>
       <c r="T12" t="n">
         <v>-0.187</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5367</v>
+        <v>-2.7586</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7054</v>
+        <v>-3.0115</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1688</v>
+        <v>0.2529</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7308</v>
@@ -1468,13 +1468,13 @@
         <v>0.3968</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1185</v>
+        <v>-0.1035</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2438</v>
+        <v>-0.0623</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1253</v>
+        <v>-0.0412</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3373</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.847</v>
+        <v>18.1586</v>
       </c>
       <c r="E14" t="n">
-        <v>6.041399999999999</v>
+        <v>6.353</v>
       </c>
       <c r="F14" t="n">
-        <v>11.8058</v>
+        <v>11.8055</v>
       </c>
       <c r="G14" t="n">
         <v>9.7532</v>
@@ -1546,13 +1546,13 @@
         <v>11.9031</v>
       </c>
       <c r="S14" t="n">
-        <v>7.878599999999999</v>
+        <v>8.1904</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7865</v>
+        <v>2.098100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>6.0924</v>
+        <v>6.0922</v>
       </c>
       <c r="V14" t="n">
         <v>2.199</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2206</v>
+        <v>1.1171</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2298</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4504</v>
+        <v>0.4704</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2391</v>
+        <v>-0.6682</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6887</v>
+        <v>0.4835</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9278</v>
+        <v>-1.1517</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0142</v>
+        <v>1.4515</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2659</v>
+        <v>1.4113</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2801</v>
+        <v>0.0402</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2249</v>
+        <v>-2.1197</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4228</v>
+        <v>-0.9278</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.1918</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9953</v>
+        <v>-0.3556</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5103</v>
+        <v>-0.8048</v>
       </c>
       <c r="U15" t="n">
-        <v>0.485</v>
+        <v>0.4491</v>
       </c>
       <c r="V15" t="n">
-        <v>0.266</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.5538999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8951</v>
+        <v>0.4775</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3406</v>
+        <v>-0.74</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5545</v>
+        <v>1.2175</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6682</v>
+        <v>-0.2391</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4835</v>
+        <v>1.6887</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1517</v>
+        <v>-1.9278</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4515</v>
+        <v>-0.0142</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4113</v>
+        <v>1.2659</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0402</v>
+        <v>-1.2801</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1197</v>
+        <v>-0.2249</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9278</v>
+        <v>0.4228</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1918</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5776</v>
+        <v>0.2522</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1109</v>
+        <v>0.0001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5333</v>
+        <v>0.2521</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.266</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5538999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0717</v>
+        <v>0.2715</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.3032</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0274</v>
+        <v>-0.0317</v>
       </c>
       <c r="G17" t="n">
         <v>0.6636</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3179</v>
+        <v>-1.118</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9352</v>
+        <v>-0.7311</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3827</v>
+        <v>-0.3869</v>
       </c>
       <c r="V17" t="n">
         <v>-0.266</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0609</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4364</v>
+        <v>0.5385</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4974</v>
+        <v>-0.4413</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1044</v>
@@ -1858,13 +1858,13 @@
         <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1111</v>
+        <v>0.2692</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0737</v>
+        <v>0.1757</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0374</v>
+        <v>0.0935</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2268</v>
+        <v>0.0172</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0365</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1903</v>
+        <v>0.0537</v>
       </c>
       <c r="G19" t="n">
         <v>1.2823</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="T19" t="n">
         <v>-0.4988</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3475</v>
+        <v>-0.1035</v>
       </c>
       <c r="V19" t="n">
         <v>-0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2001</v>
+        <v>-0.7997</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8008</v>
+        <v>-0.5967</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3993</v>
+        <v>-0.203</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1707</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.099</v>
+        <v>-0.6986</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6121</v>
+        <v>-0.408</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4869</v>
+        <v>-0.2905</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1206</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7011</v>
+        <v>-1.7555</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6998</v>
+        <v>-0.8018</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0013</v>
+        <v>-0.9537</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3988</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6314</v>
+        <v>-0.6858</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.68</v>
+        <v>-0.7821</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0486</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8114</v>
+        <v>-2.1353</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.34</v>
+        <v>-1.7481</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4714</v>
+        <v>-0.3872</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8465</v>
@@ -2170,13 +2170,13 @@
         <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1639</v>
+        <v>-0.1601</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3175</v>
+        <v>-0.0906</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1536</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1957</v>
+        <v>-2.4295</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0264</v>
+        <v>-0.4837</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2221</v>
+        <v>-1.9458</v>
       </c>
       <c r="G23" t="n">
         <v>-5.3703</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1728</v>
+        <v>-0.4066</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0001</v>
+        <v>-0.51</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.173</v>
+        <v>0.1034</v>
       </c>
       <c r="V23" t="n">
         <v>1.7603</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9019</v>
+        <v>-3.5295</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4597</v>
+        <v>-2.2556</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4423</v>
+        <v>-1.274</v>
       </c>
       <c r="G24" t="n">
         <v>0.3454</v>
@@ -2326,13 +2326,13 @@
         <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4522</v>
+        <v>-1.0798</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1222</v>
+        <v>-0.9182</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3299</v>
+        <v>-0.1616</v>
       </c>
       <c r="V24" t="n">
         <v>-2.0016</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1955</v>
+        <v>-3.7372</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7805</v>
+        <v>-3.6785</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.415</v>
+        <v>-0.0587</v>
       </c>
       <c r="G25" t="n">
         <v>2.3178</v>
@@ -2404,13 +2404,13 @@
         <v>1.5871</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.1488</v>
+        <v>-1.6905</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3716</v>
+        <v>-1.2696</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7772</v>
+        <v>-0.421</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.741</v>
+        <v>-4.0804</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.3613</v>
+        <v>-2.9532</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3797</v>
+        <v>-1.1272</v>
       </c>
       <c r="G26" t="n">
         <v>-3.5641</v>
@@ -2482,13 +2482,13 @@
         <v>1.5871</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9029</v>
+        <v>-0.2423</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6631</v>
+        <v>-0.255</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2398</v>
+        <v>0.0127</v>
       </c>
       <c r="V26" t="n">
         <v>-0.8692</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-17.847</v>
+        <v>-16.4866</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.8059</v>
+        <v>-11.8057</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.0413</v>
+        <v>-4.681</v>
       </c>
       <c r="G27" t="n">
         <v>-9.753</v>
@@ -2560,13 +2560,13 @@
         <v>13.8871</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.8786</v>
+        <v>-6.5182</v>
       </c>
       <c r="T27" t="n">
-        <v>-6.0923</v>
+        <v>-6.0924</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.7863</v>
+        <v>-0.4259999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-2.1991</v>
